--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_11-03-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_11-03-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="261">
   <si>
     <t>SKU</t>
   </si>
@@ -616,6 +616,48 @@
     <t>£727.5</t>
   </si>
   <si>
+    <t>£20.11</t>
+  </si>
+  <si>
+    <t>£21.74</t>
+  </si>
+  <si>
+    <t>£25.31</t>
+  </si>
+  <si>
+    <t>£28.79</t>
+  </si>
+  <si>
+    <t>£32.41</t>
+  </si>
+  <si>
+    <t>£42.60</t>
+  </si>
+  <si>
+    <t>£58.12</t>
+  </si>
+  <si>
+    <t>£69.47</t>
+  </si>
+  <si>
+    <t>£81.47</t>
+  </si>
+  <si>
+    <t>£86.41</t>
+  </si>
+  <si>
+    <t>£90.32</t>
+  </si>
+  <si>
+    <t>£88.72</t>
+  </si>
+  <si>
+    <t>£476.10</t>
+  </si>
+  <si>
+    <t>£515.52</t>
+  </si>
+  <si>
     <t>£12.07</t>
   </si>
   <si>
@@ -673,6 +715,9 @@
     <t>£12.16</t>
   </si>
   <si>
+    <t>£14.88</t>
+  </si>
+  <si>
     <t>£15.93</t>
   </si>
   <si>
@@ -701,9 +746,6 @@
   </si>
   <si>
     <t>£38.92</t>
-  </si>
-  <si>
-    <t>£39.81</t>
   </si>
   <si>
     <t>£11.17</t>
@@ -1212,7 +1254,7 @@
         <v>185</v>
       </c>
       <c r="N2" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="O2" t="s">
         <v>66</v>
@@ -1221,10 +1263,10 @@
         <v>88</v>
       </c>
       <c r="Q2" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="R2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1268,19 +1310,19 @@
         <v>186</v>
       </c>
       <c r="N3" t="s">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="O3" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="P3" t="s">
         <v>88</v>
       </c>
       <c r="Q3" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="R3" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1324,19 +1366,19 @@
         <v>187</v>
       </c>
       <c r="N4" t="s">
-        <v>88</v>
+        <v>202</v>
       </c>
       <c r="O4" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="P4" t="s">
         <v>88</v>
       </c>
       <c r="Q4" t="s">
-        <v>88</v>
+        <v>233</v>
       </c>
       <c r="R4" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1380,7 +1422,7 @@
         <v>188</v>
       </c>
       <c r="N5" t="s">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="O5" t="s">
         <v>69</v>
@@ -1389,10 +1431,10 @@
         <v>88</v>
       </c>
       <c r="Q5" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="R5" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1436,19 +1478,19 @@
         <v>189</v>
       </c>
       <c r="N6" t="s">
-        <v>88</v>
+        <v>204</v>
       </c>
       <c r="O6" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="P6" t="s">
         <v>88</v>
       </c>
       <c r="Q6" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="R6" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1495,16 +1537,16 @@
         <v>88</v>
       </c>
       <c r="O7" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="P7" t="s">
         <v>88</v>
       </c>
       <c r="Q7" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="R7" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1548,19 +1590,19 @@
         <v>191</v>
       </c>
       <c r="N8" t="s">
-        <v>88</v>
+        <v>205</v>
       </c>
       <c r="O8" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="P8" t="s">
         <v>88</v>
       </c>
       <c r="Q8" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="R8" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1607,16 +1649,16 @@
         <v>88</v>
       </c>
       <c r="O9" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="P9" t="s">
         <v>88</v>
       </c>
       <c r="Q9" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="R9" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1663,16 +1705,16 @@
         <v>88</v>
       </c>
       <c r="O10" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="P10" t="s">
         <v>88</v>
       </c>
       <c r="Q10" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="R10" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1716,19 +1758,19 @@
         <v>193</v>
       </c>
       <c r="N11" t="s">
-        <v>88</v>
+        <v>206</v>
       </c>
       <c r="O11" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="P11" t="s">
         <v>88</v>
       </c>
       <c r="Q11" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="R11" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1775,13 +1817,13 @@
         <v>88</v>
       </c>
       <c r="O12" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="P12" t="s">
         <v>88</v>
       </c>
       <c r="Q12" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="R12" t="s">
         <v>89</v>
@@ -1828,19 +1870,19 @@
         <v>195</v>
       </c>
       <c r="N13" t="s">
-        <v>88</v>
+        <v>207</v>
       </c>
       <c r="O13" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="P13" t="s">
         <v>88</v>
       </c>
       <c r="Q13" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="R13" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1887,13 +1929,13 @@
         <v>88</v>
       </c>
       <c r="O14" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="P14" t="s">
         <v>88</v>
       </c>
       <c r="Q14" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="R14" t="s">
         <v>89</v>
@@ -1940,16 +1982,16 @@
         <v>197</v>
       </c>
       <c r="N15" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="O15" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="P15" t="s">
         <v>88</v>
       </c>
       <c r="Q15" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="R15" t="s">
         <v>89</v>
@@ -1996,7 +2038,7 @@
         <v>198</v>
       </c>
       <c r="N16" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="O16" t="s">
         <v>79</v>
@@ -2005,10 +2047,10 @@
         <v>88</v>
       </c>
       <c r="Q16" t="s">
-        <v>229</v>
+        <v>88</v>
       </c>
       <c r="R16" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2108,10 +2150,10 @@
         <v>89</v>
       </c>
       <c r="N18" t="s">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="O18" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="P18" t="s">
         <v>88</v>
@@ -2120,7 +2162,7 @@
         <v>89</v>
       </c>
       <c r="R18" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2164,10 +2206,10 @@
         <v>89</v>
       </c>
       <c r="N19" t="s">
-        <v>88</v>
+        <v>211</v>
       </c>
       <c r="O19" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="P19" t="s">
         <v>88</v>
@@ -2176,7 +2218,7 @@
         <v>89</v>
       </c>
       <c r="R19" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2388,10 +2430,10 @@
         <v>199</v>
       </c>
       <c r="N23" t="s">
-        <v>88</v>
+        <v>212</v>
       </c>
       <c r="O23" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="P23" t="s">
         <v>89</v>
@@ -2400,7 +2442,7 @@
         <v>89</v>
       </c>
       <c r="R23" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2447,7 +2489,7 @@
         <v>88</v>
       </c>
       <c r="O24" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="P24" t="s">
         <v>89</v>
@@ -2456,7 +2498,7 @@
         <v>89</v>
       </c>
       <c r="R24" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2500,10 +2542,10 @@
         <v>88</v>
       </c>
       <c r="N25" t="s">
-        <v>88</v>
+        <v>213</v>
       </c>
       <c r="O25" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="P25" t="s">
         <v>89</v>
@@ -2512,7 +2554,7 @@
         <v>89</v>
       </c>
       <c r="R25" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
